--- a/Autism_Resources_by_State.xlsx
+++ b/Autism_Resources_by_State.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CJ\Documents\My Projects\autism_resources_by_state\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CJ\Documents\My Projects\Spectrum Works Projects\autism_resources_by_state\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB0CB7B-F579-47B9-9177-0AC1629879C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B4EB5C-DD61-4D68-8DA1-0D332E0D5685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="984" windowWidth="13284" windowHeight="13416" xr2:uid="{BB264F5C-C314-4413-9F4B-48BA520C8538}"/>
+    <workbookView xWindow="3168" yWindow="264" windowWidth="13284" windowHeight="13416" xr2:uid="{BB264F5C-C314-4413-9F4B-48BA520C8538}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -556,9 +556,6 @@
     <t>https://www.thecolorofautism.org/</t>
   </si>
   <si>
-    <t>Asperger/Autism Network (AANE)</t>
-  </si>
-  <si>
     <t>Autistic Self Advocacy Network (ASAN)</t>
   </si>
   <si>
@@ -1559,6 +1556,9 @@
   </si>
   <si>
     <t>DVRS_OR_DDD</t>
+  </si>
+  <si>
+    <t>Association for Autism and Neurodiversity (AANE)</t>
   </si>
 </sst>
 </file>
@@ -1603,11 +1603,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1986,18 +1985,18 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B2" t="s">
         <v>387</v>
-      </c>
-      <c r="B2" t="s">
-        <v>388</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -2005,17 +2004,17 @@
       <c r="D2" t="b">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="b">
+      <c r="E2" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B3" t="s">
         <v>389</v>
-      </c>
-      <c r="B3" t="s">
-        <v>390</v>
       </c>
       <c r="C3" t="s">
         <v>115</v>
@@ -2023,17 +2022,17 @@
       <c r="D3" t="b">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="b">
+      <c r="E3" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C4" t="s">
         <v>116</v>
@@ -2041,17 +2040,17 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="b">
+      <c r="E4" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C5" t="s">
         <v>117</v>
@@ -2059,17 +2058,17 @@
       <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="b">
+      <c r="E5" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C6" t="s">
         <v>118</v>
@@ -2077,17 +2076,17 @@
       <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="b">
+      <c r="E6" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>391</v>
+      </c>
+      <c r="B7" t="s">
         <v>392</v>
-      </c>
-      <c r="B7" t="s">
-        <v>393</v>
       </c>
       <c r="C7" t="s">
         <v>119</v>
@@ -2095,17 +2094,17 @@
       <c r="D7" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="b">
+      <c r="E7" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" t="s">
         <v>187</v>
-      </c>
-      <c r="B8" t="s">
-        <v>188</v>
       </c>
       <c r="C8" t="s">
         <v>120</v>
@@ -2113,17 +2112,17 @@
       <c r="D8" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="3" t="b">
+      <c r="E8" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>393</v>
+      </c>
+      <c r="B9" t="s">
         <v>394</v>
-      </c>
-      <c r="B9" t="s">
-        <v>395</v>
       </c>
       <c r="C9" t="s">
         <v>121</v>
@@ -2131,17 +2130,17 @@
       <c r="D9" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="3" t="b">
+      <c r="E9" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>395</v>
+      </c>
+      <c r="B10" t="s">
         <v>396</v>
-      </c>
-      <c r="B10" t="s">
-        <v>397</v>
       </c>
       <c r="C10" t="s">
         <v>122</v>
@@ -2149,17 +2148,17 @@
       <c r="D10" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="3" t="b">
+      <c r="E10" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" t="s">
         <v>195</v>
-      </c>
-      <c r="B11" t="s">
-        <v>196</v>
       </c>
       <c r="C11" t="s">
         <v>124</v>
@@ -2167,17 +2166,17 @@
       <c r="D11" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="3" t="b">
+      <c r="E11" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C12" t="s">
         <v>125</v>
@@ -2185,17 +2184,17 @@
       <c r="D12" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="3" t="b">
+      <c r="E12" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>400</v>
+      </c>
+      <c r="B13" t="s">
         <v>401</v>
-      </c>
-      <c r="B13" t="s">
-        <v>402</v>
       </c>
       <c r="C13" t="s">
         <v>126</v>
@@ -2203,17 +2202,17 @@
       <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="3" t="b">
+      <c r="E13" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>404</v>
+      </c>
+      <c r="B14" t="s">
         <v>405</v>
-      </c>
-      <c r="B14" t="s">
-        <v>406</v>
       </c>
       <c r="C14" t="s">
         <v>128</v>
@@ -2221,17 +2220,17 @@
       <c r="D14" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="b">
+      <c r="E14" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>406</v>
+      </c>
+      <c r="B15" t="s">
         <v>407</v>
-      </c>
-      <c r="B15" t="s">
-        <v>408</v>
       </c>
       <c r="C15" t="s">
         <v>129</v>
@@ -2239,17 +2238,17 @@
       <c r="D15" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="3" t="b">
+      <c r="E15" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>408</v>
+      </c>
+      <c r="B16" t="s">
         <v>409</v>
-      </c>
-      <c r="B16" t="s">
-        <v>410</v>
       </c>
       <c r="C16" t="s">
         <v>130</v>
@@ -2257,17 +2256,17 @@
       <c r="D16" t="b">
         <v>1</v>
       </c>
-      <c r="E16" s="3" t="b">
+      <c r="E16" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B17" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C17" t="s">
         <v>131</v>
@@ -2275,17 +2274,17 @@
       <c r="D17" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="3" t="b">
+      <c r="E17" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>413</v>
+      </c>
+      <c r="B18" t="s">
         <v>414</v>
-      </c>
-      <c r="B18" t="s">
-        <v>415</v>
       </c>
       <c r="C18" t="s">
         <v>133</v>
@@ -2293,17 +2292,17 @@
       <c r="D18" t="b">
         <v>1</v>
       </c>
-      <c r="E18" s="3" t="b">
+      <c r="E18" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B19" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C19" t="s">
         <v>134</v>
@@ -2311,17 +2310,17 @@
       <c r="D19" t="b">
         <v>1</v>
       </c>
-      <c r="E19" s="3" t="b">
+      <c r="E19" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B20" t="s">
         <v>417</v>
-      </c>
-      <c r="B20" t="s">
-        <v>418</v>
       </c>
       <c r="C20" t="s">
         <v>135</v>
@@ -2329,17 +2328,17 @@
       <c r="D20" t="b">
         <v>1</v>
       </c>
-      <c r="E20" s="3" t="b">
+      <c r="E20" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>418</v>
+      </c>
+      <c r="B21" t="s">
         <v>419</v>
-      </c>
-      <c r="B21" t="s">
-        <v>420</v>
       </c>
       <c r="C21" t="s">
         <v>136</v>
@@ -2347,17 +2346,17 @@
       <c r="D21" t="b">
         <v>1</v>
       </c>
-      <c r="E21" s="3" t="b">
+      <c r="E21" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>420</v>
+      </c>
+      <c r="B22" t="s">
         <v>421</v>
-      </c>
-      <c r="B22" t="s">
-        <v>422</v>
       </c>
       <c r="C22" t="s">
         <v>137</v>
@@ -2365,17 +2364,17 @@
       <c r="D22" t="b">
         <v>1</v>
       </c>
-      <c r="E22" s="3" t="b">
+      <c r="E22" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B23" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C23" t="s">
         <v>138</v>
@@ -2383,17 +2382,17 @@
       <c r="D23" t="b">
         <v>1</v>
       </c>
-      <c r="E23" s="3" t="b">
+      <c r="E23" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C24" t="s">
         <v>139</v>
@@ -2401,17 +2400,17 @@
       <c r="D24" t="b">
         <v>1</v>
       </c>
-      <c r="E24" s="3" t="b">
+      <c r="E24" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>424</v>
+      </c>
+      <c r="B25" t="s">
         <v>425</v>
-      </c>
-      <c r="B25" t="s">
-        <v>426</v>
       </c>
       <c r="C25" t="s">
         <v>140</v>
@@ -2419,17 +2418,17 @@
       <c r="D25" t="b">
         <v>1</v>
       </c>
-      <c r="E25" s="3" t="b">
+      <c r="E25" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>426</v>
+      </c>
+      <c r="B26" t="s">
         <v>427</v>
-      </c>
-      <c r="B26" t="s">
-        <v>428</v>
       </c>
       <c r="C26" t="s">
         <v>141</v>
@@ -2437,17 +2436,17 @@
       <c r="D26" t="b">
         <v>1</v>
       </c>
-      <c r="E26" s="3" t="b">
+      <c r="E26" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>428</v>
+      </c>
+      <c r="B27" t="s">
         <v>429</v>
-      </c>
-      <c r="B27" t="s">
-        <v>430</v>
       </c>
       <c r="C27" t="s">
         <v>142</v>
@@ -2455,17 +2454,17 @@
       <c r="D27" t="b">
         <v>1</v>
       </c>
-      <c r="E27" s="3" t="b">
+      <c r="E27" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>430</v>
+      </c>
+      <c r="B28" t="s">
         <v>431</v>
-      </c>
-      <c r="B28" t="s">
-        <v>432</v>
       </c>
       <c r="C28" t="s">
         <v>143</v>
@@ -2473,17 +2472,17 @@
       <c r="D28" t="b">
         <v>1</v>
       </c>
-      <c r="E28" s="3" t="b">
+      <c r="E28" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>432</v>
+      </c>
+      <c r="B29" t="s">
         <v>433</v>
-      </c>
-      <c r="B29" t="s">
-        <v>434</v>
       </c>
       <c r="C29" t="s">
         <v>144</v>
@@ -2491,17 +2490,17 @@
       <c r="D29" t="b">
         <v>1</v>
       </c>
-      <c r="E29" s="3" t="b">
+      <c r="E29" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>436</v>
+      </c>
+      <c r="B30" t="s">
         <v>437</v>
-      </c>
-      <c r="B30" t="s">
-        <v>438</v>
       </c>
       <c r="C30" t="s">
         <v>146</v>
@@ -2509,17 +2508,17 @@
       <c r="D30" t="b">
         <v>1</v>
       </c>
-      <c r="E30" s="3" t="b">
+      <c r="E30" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B31" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C31" t="s">
         <v>147</v>
@@ -2527,17 +2526,17 @@
       <c r="D31" t="b">
         <v>1</v>
       </c>
-      <c r="E31" s="3" t="b">
+      <c r="E31" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C32" t="s">
         <v>148</v>
@@ -2545,17 +2544,17 @@
       <c r="D32" t="b">
         <v>1</v>
       </c>
-      <c r="E32" s="3" t="b">
+      <c r="E32" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>439</v>
+      </c>
+      <c r="B33" t="s">
         <v>440</v>
-      </c>
-      <c r="B33" t="s">
-        <v>441</v>
       </c>
       <c r="C33" t="s">
         <v>149</v>
@@ -2563,17 +2562,17 @@
       <c r="D33" t="b">
         <v>1</v>
       </c>
-      <c r="E33" s="3" t="b">
+      <c r="E33" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B34" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C34" t="s">
         <v>150</v>
@@ -2581,17 +2580,17 @@
       <c r="D34" t="b">
         <v>1</v>
       </c>
-      <c r="E34" s="3" t="b">
+      <c r="E34" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>442</v>
+      </c>
+      <c r="B35" t="s">
         <v>443</v>
-      </c>
-      <c r="B35" t="s">
-        <v>444</v>
       </c>
       <c r="C35" t="s">
         <v>151</v>
@@ -2599,17 +2598,17 @@
       <c r="D35" t="b">
         <v>1</v>
       </c>
-      <c r="E35" s="3" t="b">
+      <c r="E35" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B36" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C36" t="s">
         <v>152</v>
@@ -2617,17 +2616,17 @@
       <c r="D36" t="b">
         <v>1</v>
       </c>
-      <c r="E36" s="3" t="b">
+      <c r="E36" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>445</v>
+      </c>
+      <c r="B37" t="s">
         <v>446</v>
-      </c>
-      <c r="B37" t="s">
-        <v>447</v>
       </c>
       <c r="C37" t="s">
         <v>153</v>
@@ -2635,17 +2634,17 @@
       <c r="D37" t="b">
         <v>1</v>
       </c>
-      <c r="E37" s="3" t="b">
+      <c r="E37" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>449</v>
+      </c>
+      <c r="B38" t="s">
         <v>450</v>
-      </c>
-      <c r="B38" t="s">
-        <v>451</v>
       </c>
       <c r="C38" t="s">
         <v>155</v>
@@ -2653,17 +2652,17 @@
       <c r="D38" t="b">
         <v>1</v>
       </c>
-      <c r="E38" s="3" t="b">
+      <c r="E38" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B39" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C39" t="s">
         <v>156</v>
@@ -2671,17 +2670,17 @@
       <c r="D39" t="b">
         <v>1</v>
       </c>
-      <c r="E39" s="3" t="b">
+      <c r="E39" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B40" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C40" t="s">
         <v>157</v>
@@ -2689,17 +2688,17 @@
       <c r="D40" t="b">
         <v>1</v>
       </c>
-      <c r="E40" s="3" t="b">
+      <c r="E40" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>452</v>
+      </c>
+      <c r="B41" t="s">
         <v>453</v>
-      </c>
-      <c r="B41" t="s">
-        <v>454</v>
       </c>
       <c r="C41" t="s">
         <v>158</v>
@@ -2707,17 +2706,17 @@
       <c r="D41" t="b">
         <v>1</v>
       </c>
-      <c r="E41" s="3" t="b">
+      <c r="E41" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>454</v>
+      </c>
+      <c r="B42" t="s">
         <v>455</v>
-      </c>
-      <c r="B42" t="s">
-        <v>456</v>
       </c>
       <c r="C42" t="s">
         <v>159</v>
@@ -2725,17 +2724,17 @@
       <c r="D42" t="b">
         <v>1</v>
       </c>
-      <c r="E42" s="3" t="b">
+      <c r="E42" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>458</v>
+      </c>
+      <c r="B43" t="s">
         <v>459</v>
-      </c>
-      <c r="B43" t="s">
-        <v>460</v>
       </c>
       <c r="C43" t="s">
         <v>161</v>
@@ -2743,17 +2742,17 @@
       <c r="D43" t="b">
         <v>1</v>
       </c>
-      <c r="E43" s="3" t="b">
+      <c r="E43" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B44" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C44" t="s">
         <v>163</v>
@@ -2761,7 +2760,7 @@
       <c r="D44" t="b">
         <v>1</v>
       </c>
-      <c r="E44" s="3" t="b">
+      <c r="E44" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2771,7 +2770,7 @@
         <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C45" t="s">
         <v>115</v>
@@ -2779,7 +2778,7 @@
       <c r="D45" t="b">
         <v>1</v>
       </c>
-      <c r="E45" s="3" t="b">
+      <c r="E45" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2789,7 +2788,7 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C46" t="s">
         <v>116</v>
@@ -2797,7 +2796,7 @@
       <c r="D46" t="b">
         <v>1</v>
       </c>
-      <c r="E46" s="3" t="b">
+      <c r="E46" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2807,7 +2806,7 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C47" t="s">
         <v>117</v>
@@ -2815,7 +2814,7 @@
       <c r="D47" t="b">
         <v>1</v>
       </c>
-      <c r="E47" s="3" t="b">
+      <c r="E47" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2825,7 +2824,7 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C48" t="s">
         <v>118</v>
@@ -2833,7 +2832,7 @@
       <c r="D48" t="b">
         <v>1</v>
       </c>
-      <c r="E48" s="3" t="b">
+      <c r="E48" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2843,7 +2842,7 @@
         <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C49" t="s">
         <v>119</v>
@@ -2851,7 +2850,7 @@
       <c r="D49" t="b">
         <v>1</v>
       </c>
-      <c r="E49" s="3" t="b">
+      <c r="E49" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2861,7 +2860,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C50" t="s">
         <v>121</v>
@@ -2869,7 +2868,7 @@
       <c r="D50" t="b">
         <v>1</v>
       </c>
-      <c r="E50" s="3" t="b">
+      <c r="E50" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2879,7 +2878,7 @@
         <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C51" t="s">
         <v>122</v>
@@ -2887,7 +2886,7 @@
       <c r="D51" t="b">
         <v>1</v>
       </c>
-      <c r="E51" s="3" t="b">
+      <c r="E51" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2897,7 +2896,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C52" t="s">
         <v>124</v>
@@ -2905,7 +2904,7 @@
       <c r="D52" t="b">
         <v>1</v>
       </c>
-      <c r="E52" s="3" t="b">
+      <c r="E52" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2923,7 +2922,7 @@
       <c r="D53" t="b">
         <v>1</v>
       </c>
-      <c r="E53" s="3" t="b">
+      <c r="E53" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2933,7 +2932,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C54" t="s">
         <v>126</v>
@@ -2941,7 +2940,7 @@
       <c r="D54" t="b">
         <v>1</v>
       </c>
-      <c r="E54" s="3" t="b">
+      <c r="E54" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2951,7 +2950,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C55" t="s">
         <v>128</v>
@@ -2959,7 +2958,7 @@
       <c r="D55" t="b">
         <v>1</v>
       </c>
-      <c r="E55" s="3" t="b">
+      <c r="E55" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2969,7 +2968,7 @@
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C56" t="s">
         <v>129</v>
@@ -2977,7 +2976,7 @@
       <c r="D56" t="b">
         <v>1</v>
       </c>
-      <c r="E56" s="3" t="b">
+      <c r="E56" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2987,7 +2986,7 @@
         <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C57" t="s">
         <v>130</v>
@@ -2995,7 +2994,7 @@
       <c r="D57" t="b">
         <v>1</v>
       </c>
-      <c r="E57" s="3" t="b">
+      <c r="E57" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3005,7 +3004,7 @@
         <v>53</v>
       </c>
       <c r="B58" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C58" t="s">
         <v>131</v>
@@ -3013,7 +3012,7 @@
       <c r="D58" t="b">
         <v>1</v>
       </c>
-      <c r="E58" s="3" t="b">
+      <c r="E58" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3031,7 +3030,7 @@
       <c r="D59" t="b">
         <v>1</v>
       </c>
-      <c r="E59" s="3" t="b">
+      <c r="E59" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3041,7 +3040,7 @@
         <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C60" t="s">
         <v>133</v>
@@ -3049,7 +3048,7 @@
       <c r="D60" t="b">
         <v>1</v>
       </c>
-      <c r="E60" s="3" t="b">
+      <c r="E60" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3059,7 +3058,7 @@
         <v>53</v>
       </c>
       <c r="B61" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C61" t="s">
         <v>134</v>
@@ -3067,7 +3066,7 @@
       <c r="D61" t="b">
         <v>1</v>
       </c>
-      <c r="E61" s="3" t="b">
+      <c r="E61" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3077,7 +3076,7 @@
         <v>53</v>
       </c>
       <c r="B62" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C62" t="s">
         <v>135</v>
@@ -3085,7 +3084,7 @@
       <c r="D62" t="b">
         <v>1</v>
       </c>
-      <c r="E62" s="3" t="b">
+      <c r="E62" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3095,7 +3094,7 @@
         <v>53</v>
       </c>
       <c r="B63" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C63" t="s">
         <v>136</v>
@@ -3103,7 +3102,7 @@
       <c r="D63" t="b">
         <v>1</v>
       </c>
-      <c r="E63" s="3" t="b">
+      <c r="E63" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3113,7 +3112,7 @@
         <v>53</v>
       </c>
       <c r="B64" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C64" t="s">
         <v>137</v>
@@ -3121,7 +3120,7 @@
       <c r="D64" t="b">
         <v>1</v>
       </c>
-      <c r="E64" s="3" t="b">
+      <c r="E64" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3139,7 +3138,7 @@
       <c r="D65" t="b">
         <v>1</v>
       </c>
-      <c r="E65" s="3" t="b">
+      <c r="E65" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3149,7 +3148,7 @@
         <v>53</v>
       </c>
       <c r="B66" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C66" t="s">
         <v>139</v>
@@ -3157,7 +3156,7 @@
       <c r="D66" t="b">
         <v>1</v>
       </c>
-      <c r="E66" s="3" t="b">
+      <c r="E66" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3167,7 +3166,7 @@
         <v>53</v>
       </c>
       <c r="B67" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C67" t="s">
         <v>140</v>
@@ -3175,7 +3174,7 @@
       <c r="D67" t="b">
         <v>1</v>
       </c>
-      <c r="E67" s="3" t="b">
+      <c r="E67" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3185,7 +3184,7 @@
         <v>53</v>
       </c>
       <c r="B68" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C68" t="s">
         <v>141</v>
@@ -3193,7 +3192,7 @@
       <c r="D68" t="b">
         <v>1</v>
       </c>
-      <c r="E68" s="3" t="b">
+      <c r="E68" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3211,7 +3210,7 @@
       <c r="D69" t="b">
         <v>1</v>
       </c>
-      <c r="E69" s="3" t="b">
+      <c r="E69" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3229,7 +3228,7 @@
       <c r="D70" t="b">
         <v>1</v>
       </c>
-      <c r="E70" s="3" t="b">
+      <c r="E70" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3239,7 +3238,7 @@
         <v>53</v>
       </c>
       <c r="B71" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C71" t="s">
         <v>144</v>
@@ -3247,7 +3246,7 @@
       <c r="D71" t="b">
         <v>1</v>
       </c>
-      <c r="E71" s="3" t="b">
+      <c r="E71" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3257,7 +3256,7 @@
         <v>53</v>
       </c>
       <c r="B72" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C72" t="s">
         <v>147</v>
@@ -3265,7 +3264,7 @@
       <c r="D72" t="b">
         <v>1</v>
       </c>
-      <c r="E72" s="3" t="b">
+      <c r="E72" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3275,7 +3274,7 @@
         <v>53</v>
       </c>
       <c r="B73" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C73" t="s">
         <v>148</v>
@@ -3283,7 +3282,7 @@
       <c r="D73" t="b">
         <v>1</v>
       </c>
-      <c r="E73" s="3" t="b">
+      <c r="E73" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3293,7 +3292,7 @@
         <v>53</v>
       </c>
       <c r="B74" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C74" t="s">
         <v>149</v>
@@ -3301,7 +3300,7 @@
       <c r="D74" t="b">
         <v>1</v>
       </c>
-      <c r="E74" s="3" t="b">
+      <c r="E74" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3311,7 +3310,7 @@
         <v>53</v>
       </c>
       <c r="B75" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C75" t="s">
         <v>151</v>
@@ -3319,7 +3318,7 @@
       <c r="D75" t="b">
         <v>1</v>
       </c>
-      <c r="E75" s="3" t="b">
+      <c r="E75" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3329,7 +3328,7 @@
         <v>53</v>
       </c>
       <c r="B76" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C76" t="s">
         <v>152</v>
@@ -3337,7 +3336,7 @@
       <c r="D76" t="b">
         <v>1</v>
       </c>
-      <c r="E76" s="3" t="b">
+      <c r="E76" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3347,7 +3346,7 @@
         <v>53</v>
       </c>
       <c r="B77" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C77" t="s">
         <v>153</v>
@@ -3355,7 +3354,7 @@
       <c r="D77" t="b">
         <v>1</v>
       </c>
-      <c r="E77" s="3" t="b">
+      <c r="E77" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3365,7 +3364,7 @@
         <v>53</v>
       </c>
       <c r="B78" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C78" t="s">
         <v>154</v>
@@ -3373,7 +3372,7 @@
       <c r="D78" t="b">
         <v>1</v>
       </c>
-      <c r="E78" s="3" t="b">
+      <c r="E78" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3391,7 +3390,7 @@
       <c r="D79" t="b">
         <v>1</v>
       </c>
-      <c r="E79" s="3" t="b">
+      <c r="E79" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3401,7 +3400,7 @@
         <v>53</v>
       </c>
       <c r="B80" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C80" t="s">
         <v>156</v>
@@ -3409,7 +3408,7 @@
       <c r="D80" t="b">
         <v>1</v>
       </c>
-      <c r="E80" s="3" t="b">
+      <c r="E80" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3419,7 +3418,7 @@
         <v>53</v>
       </c>
       <c r="B81" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C81" t="s">
         <v>157</v>
@@ -3427,7 +3426,7 @@
       <c r="D81" t="b">
         <v>1</v>
       </c>
-      <c r="E81" s="3" t="b">
+      <c r="E81" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3437,7 +3436,7 @@
         <v>53</v>
       </c>
       <c r="B82" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C82" t="s">
         <v>158</v>
@@ -3445,7 +3444,7 @@
       <c r="D82" t="b">
         <v>1</v>
       </c>
-      <c r="E82" s="3" t="b">
+      <c r="E82" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3455,7 +3454,7 @@
         <v>53</v>
       </c>
       <c r="B83" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C83" t="s">
         <v>159</v>
@@ -3463,7 +3462,7 @@
       <c r="D83" t="b">
         <v>1</v>
       </c>
-      <c r="E83" s="3" t="b">
+      <c r="E83" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3473,7 +3472,7 @@
         <v>53</v>
       </c>
       <c r="B84" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C84" t="s">
         <v>160</v>
@@ -3481,7 +3480,7 @@
       <c r="D84" t="b">
         <v>1</v>
       </c>
-      <c r="E84" s="3" t="b">
+      <c r="E84" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3491,7 +3490,7 @@
         <v>53</v>
       </c>
       <c r="B85" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C85" t="s">
         <v>161</v>
@@ -3499,7 +3498,7 @@
       <c r="D85" t="b">
         <v>1</v>
       </c>
-      <c r="E85" s="3" t="b">
+      <c r="E85" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3509,7 +3508,7 @@
         <v>53</v>
       </c>
       <c r="B86" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C86" t="s">
         <v>162</v>
@@ -3517,7 +3516,7 @@
       <c r="D86" t="b">
         <v>1</v>
       </c>
-      <c r="E86" s="3" t="b">
+      <c r="E86" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3527,7 +3526,7 @@
         <v>53</v>
       </c>
       <c r="B87" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C87" t="s">
         <v>163</v>
@@ -3535,7 +3534,7 @@
       <c r="D87" t="b">
         <v>1</v>
       </c>
-      <c r="E87" s="3" t="b">
+      <c r="E87" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3553,17 +3552,17 @@
       <c r="D88" t="b">
         <v>1</v>
       </c>
-      <c r="E88" s="3" t="b">
+      <c r="E88" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>397</v>
+      </c>
+      <c r="B89" t="s">
         <v>398</v>
-      </c>
-      <c r="B89" t="s">
-        <v>399</v>
       </c>
       <c r="C89" t="s">
         <v>123</v>
@@ -3571,17 +3570,17 @@
       <c r="D89" t="b">
         <v>1</v>
       </c>
-      <c r="E89" s="3" t="b">
+      <c r="E89" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>402</v>
+      </c>
+      <c r="B90" t="s">
         <v>403</v>
-      </c>
-      <c r="B90" t="s">
-        <v>404</v>
       </c>
       <c r="C90" t="s">
         <v>127</v>
@@ -3589,17 +3588,17 @@
       <c r="D90" t="b">
         <v>1</v>
       </c>
-      <c r="E90" s="3" t="b">
+      <c r="E90" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>411</v>
+      </c>
+      <c r="B91" t="s">
         <v>412</v>
-      </c>
-      <c r="B91" t="s">
-        <v>413</v>
       </c>
       <c r="C91" t="s">
         <v>132</v>
@@ -3607,17 +3606,17 @@
       <c r="D91" t="b">
         <v>1</v>
       </c>
-      <c r="E91" s="3" t="b">
+      <c r="E91" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>434</v>
+      </c>
+      <c r="B92" t="s">
         <v>435</v>
-      </c>
-      <c r="B92" t="s">
-        <v>436</v>
       </c>
       <c r="C92" t="s">
         <v>145</v>
@@ -3625,17 +3624,17 @@
       <c r="D92" t="b">
         <v>1</v>
       </c>
-      <c r="E92" s="3" t="b">
+      <c r="E92" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>447</v>
+      </c>
+      <c r="B93" t="s">
         <v>448</v>
-      </c>
-      <c r="B93" t="s">
-        <v>449</v>
       </c>
       <c r="C93" t="s">
         <v>154</v>
@@ -3643,17 +3642,17 @@
       <c r="D93" t="b">
         <v>1</v>
       </c>
-      <c r="E93" s="3" t="b">
+      <c r="E93" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>456</v>
+      </c>
+      <c r="B94" t="s">
         <v>457</v>
-      </c>
-      <c r="B94" t="s">
-        <v>458</v>
       </c>
       <c r="C94" t="s">
         <v>160</v>
@@ -3661,17 +3660,17 @@
       <c r="D94" t="b">
         <v>1</v>
       </c>
-      <c r="E94" s="3" t="b">
+      <c r="E94" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B95" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C95" t="s">
         <v>162</v>
@@ -3679,17 +3678,17 @@
       <c r="D95" t="b">
         <v>1</v>
       </c>
-      <c r="E95" s="3" t="b">
+      <c r="E95" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B96" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C96" t="s">
         <v>13</v>
@@ -3697,7 +3696,7 @@
       <c r="D96" t="b">
         <v>1</v>
       </c>
-      <c r="E96" s="3" t="b">
+      <c r="E96" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -3707,7 +3706,7 @@
         <v>53</v>
       </c>
       <c r="B97" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C97" t="s">
         <v>120</v>
@@ -3715,7 +3714,7 @@
       <c r="D97" t="b">
         <v>1</v>
       </c>
-      <c r="E97" s="3" t="b">
+      <c r="E97" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -3725,7 +3724,7 @@
         <v>53</v>
       </c>
       <c r="B98" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C98" t="s">
         <v>123</v>
@@ -3733,7 +3732,7 @@
       <c r="D98" t="b">
         <v>1</v>
       </c>
-      <c r="E98" s="3" t="b">
+      <c r="E98" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -3743,7 +3742,7 @@
         <v>53</v>
       </c>
       <c r="B99" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C99" t="s">
         <v>127</v>
@@ -3751,7 +3750,7 @@
       <c r="D99" t="b">
         <v>1</v>
       </c>
-      <c r="E99" s="3" t="b">
+      <c r="E99" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -3763,7 +3762,7 @@
       <c r="D100" t="b">
         <v>1</v>
       </c>
-      <c r="E100" s="3" t="b">
+      <c r="E100" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -3773,7 +3772,7 @@
         <v>53</v>
       </c>
       <c r="B101" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C101" t="s">
         <v>145</v>
@@ -3781,7 +3780,7 @@
       <c r="D101" t="b">
         <v>1</v>
       </c>
-      <c r="E101" s="3" t="b">
+      <c r="E101" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -3799,7 +3798,7 @@
       <c r="D102" t="b">
         <v>1</v>
       </c>
-      <c r="E102" s="3" t="b">
+      <c r="E102" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -3814,7 +3813,7 @@
       <c r="C103" t="s">
         <v>2</v>
       </c>
-      <c r="E103" s="3" t="b">
+      <c r="E103" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3829,7 +3828,7 @@
       <c r="C104" t="s">
         <v>116</v>
       </c>
-      <c r="E104" s="3" t="b">
+      <c r="E104" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3844,7 +3843,7 @@
       <c r="C105" t="s">
         <v>117</v>
       </c>
-      <c r="E105" s="3" t="b">
+      <c r="E105" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3859,7 +3858,7 @@
       <c r="C106" t="s">
         <v>119</v>
       </c>
-      <c r="E106" s="3" t="b">
+      <c r="E106" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3874,7 +3873,7 @@
       <c r="C107" t="s">
         <v>121</v>
       </c>
-      <c r="E107" s="3" t="b">
+      <c r="E107" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3889,7 +3888,7 @@
       <c r="C108" t="s">
         <v>122</v>
       </c>
-      <c r="E108" s="3" t="b">
+      <c r="E108" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3904,7 +3903,7 @@
       <c r="C109" t="s">
         <v>22</v>
       </c>
-      <c r="E109" s="3" t="b">
+      <c r="E109" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3919,7 +3918,7 @@
       <c r="C110" t="s">
         <v>123</v>
       </c>
-      <c r="E110" s="3" t="b">
+      <c r="E110" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3934,7 +3933,7 @@
       <c r="C111" t="s">
         <v>124</v>
       </c>
-      <c r="E111" s="3" t="b">
+      <c r="E111" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3949,7 +3948,7 @@
       <c r="C112" t="s">
         <v>125</v>
       </c>
-      <c r="E112" s="3" t="b">
+      <c r="E112" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3964,7 +3963,7 @@
       <c r="C113" t="s">
         <v>126</v>
       </c>
-      <c r="E113" s="3" t="b">
+      <c r="E113" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3979,7 +3978,7 @@
       <c r="C114" t="s">
         <v>128</v>
       </c>
-      <c r="E114" s="3" t="b">
+      <c r="E114" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -3994,7 +3993,7 @@
       <c r="C115" t="s">
         <v>130</v>
       </c>
-      <c r="E115" s="3" t="b">
+      <c r="E115" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4009,7 +4008,7 @@
       <c r="C116" t="s">
         <v>132</v>
       </c>
-      <c r="E116" s="3" t="b">
+      <c r="E116" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4024,7 +4023,7 @@
       <c r="C117" t="s">
         <v>133</v>
       </c>
-      <c r="E117" s="3" t="b">
+      <c r="E117" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4039,7 +4038,7 @@
       <c r="C118" t="s">
         <v>134</v>
       </c>
-      <c r="E118" s="3" t="b">
+      <c r="E118" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4054,7 +4053,7 @@
       <c r="C119" t="s">
         <v>135</v>
       </c>
-      <c r="E119" s="3" t="b">
+      <c r="E119" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4069,7 +4068,7 @@
       <c r="C120" t="s">
         <v>136</v>
       </c>
-      <c r="E120" s="3" t="b">
+      <c r="E120" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4084,7 +4083,7 @@
       <c r="C121" t="s">
         <v>137</v>
       </c>
-      <c r="E121" s="3" t="b">
+      <c r="E121" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4099,7 +4098,7 @@
       <c r="C122" t="s">
         <v>138</v>
       </c>
-      <c r="E122" s="3" t="b">
+      <c r="E122" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4114,7 +4113,7 @@
       <c r="C123" t="s">
         <v>139</v>
       </c>
-      <c r="E123" s="3" t="b">
+      <c r="E123" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4129,7 +4128,7 @@
       <c r="C124" t="s">
         <v>140</v>
       </c>
-      <c r="E124" s="3" t="b">
+      <c r="E124" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4144,7 +4143,7 @@
       <c r="C125" t="s">
         <v>141</v>
       </c>
-      <c r="E125" s="3" t="b">
+      <c r="E125" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4159,7 +4158,7 @@
       <c r="C126" t="s">
         <v>142</v>
       </c>
-      <c r="E126" s="3" t="b">
+      <c r="E126" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4174,7 +4173,7 @@
       <c r="C127" t="s">
         <v>143</v>
       </c>
-      <c r="E127" s="3" t="b">
+      <c r="E127" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4189,7 +4188,7 @@
       <c r="C128" t="s">
         <v>145</v>
       </c>
-      <c r="E128" s="3" t="b">
+      <c r="E128" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4204,7 +4203,7 @@
       <c r="C129" t="s">
         <v>146</v>
       </c>
-      <c r="E129" s="3" t="b">
+      <c r="E129" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4219,7 +4218,7 @@
       <c r="C130" t="s">
         <v>147</v>
       </c>
-      <c r="E130" s="3" t="b">
+      <c r="E130" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4234,7 +4233,7 @@
       <c r="C131" t="s">
         <v>148</v>
       </c>
-      <c r="E131" s="3" t="b">
+      <c r="E131" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4249,7 +4248,7 @@
       <c r="C132" t="s">
         <v>149</v>
       </c>
-      <c r="E132" s="3" t="b">
+      <c r="E132" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4264,7 +4263,7 @@
       <c r="C133" t="s">
         <v>151</v>
       </c>
-      <c r="E133" s="3" t="b">
+      <c r="E133" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4279,7 +4278,7 @@
       <c r="C134" t="s">
         <v>154</v>
       </c>
-      <c r="E134" s="3" t="b">
+      <c r="E134" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4294,7 +4293,7 @@
       <c r="C135" t="s">
         <v>155</v>
       </c>
-      <c r="E135" s="3" t="b">
+      <c r="E135" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4309,7 +4308,7 @@
       <c r="C136" t="s">
         <v>156</v>
       </c>
-      <c r="E136" s="3" t="b">
+      <c r="E136" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4324,7 +4323,7 @@
       <c r="C137" t="s">
         <v>157</v>
       </c>
-      <c r="E137" s="3" t="b">
+      <c r="E137" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4339,7 +4338,7 @@
       <c r="C138" t="s">
         <v>158</v>
       </c>
-      <c r="E138" s="3" t="b">
+      <c r="E138" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4354,7 +4353,7 @@
       <c r="C139" t="s">
         <v>159</v>
       </c>
-      <c r="E139" s="3" t="b">
+      <c r="E139" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4369,7 +4368,7 @@
       <c r="C140" t="s">
         <v>160</v>
       </c>
-      <c r="E140" s="3" t="b">
+      <c r="E140" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4384,7 +4383,7 @@
       <c r="C141" t="s">
         <v>13</v>
       </c>
-      <c r="E141" s="3" t="b">
+      <c r="E141" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4399,7 +4398,7 @@
       <c r="C142" t="s">
         <v>62</v>
       </c>
-      <c r="E142" s="3" t="b">
+      <c r="E142" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4414,7 +4413,7 @@
       <c r="C143" t="s">
         <v>63</v>
       </c>
-      <c r="E143" s="3" t="b">
+      <c r="E143" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -4424,807 +4423,807 @@
         <v>164</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C144" t="s">
         <v>2</v>
       </c>
-      <c r="E144" s="3" t="b">
+      <c r="E144" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>177</v>
+      </c>
+      <c r="B145" t="s">
         <v>178</v>
-      </c>
-      <c r="B145" t="s">
-        <v>179</v>
       </c>
       <c r="C145" t="s">
         <v>115</v>
       </c>
-      <c r="E145" s="3" t="b">
+      <c r="E145" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
+        <v>179</v>
+      </c>
+      <c r="B146" t="s">
         <v>180</v>
-      </c>
-      <c r="B146" t="s">
-        <v>181</v>
       </c>
       <c r="C146" t="s">
         <v>116</v>
       </c>
-      <c r="E146" s="3" t="b">
+      <c r="E146" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B147" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C147" t="s">
         <v>117</v>
       </c>
-      <c r="E147" s="3" t="b">
+      <c r="E147" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B148" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C148" t="s">
         <v>118</v>
       </c>
-      <c r="E148" s="3" t="b">
+      <c r="E148" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
+        <v>184</v>
+      </c>
+      <c r="B149" t="s">
         <v>185</v>
-      </c>
-      <c r="B149" t="s">
-        <v>186</v>
       </c>
       <c r="C149" t="s">
         <v>119</v>
       </c>
-      <c r="E149" s="3" t="b">
+      <c r="E149" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
+        <v>186</v>
+      </c>
+      <c r="B150" t="s">
         <v>187</v>
-      </c>
-      <c r="B150" t="s">
-        <v>188</v>
       </c>
       <c r="C150" t="s">
         <v>120</v>
       </c>
-      <c r="E150" s="3" t="b">
+      <c r="E150" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B151" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C151" t="s">
         <v>121</v>
       </c>
-      <c r="E151" s="3" t="b">
+      <c r="E151" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
+        <v>190</v>
+      </c>
+      <c r="B152" t="s">
         <v>191</v>
-      </c>
-      <c r="B152" t="s">
-        <v>192</v>
       </c>
       <c r="C152" t="s">
         <v>122</v>
       </c>
-      <c r="E152" s="3" t="b">
+      <c r="E152" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>192</v>
+      </c>
+      <c r="B153" t="s">
         <v>193</v>
-      </c>
-      <c r="B153" t="s">
-        <v>194</v>
       </c>
       <c r="C153" t="s">
         <v>22</v>
       </c>
-      <c r="E153" s="3" t="b">
+      <c r="E153" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>379</v>
+      </c>
+      <c r="B154" t="s">
         <v>380</v>
-      </c>
-      <c r="B154" t="s">
-        <v>381</v>
       </c>
       <c r="C154" t="s">
         <v>123</v>
       </c>
-      <c r="E154" s="3" t="b">
+      <c r="E154" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>194</v>
+      </c>
+      <c r="B155" t="s">
         <v>195</v>
-      </c>
-      <c r="B155" t="s">
-        <v>196</v>
       </c>
       <c r="C155" t="s">
         <v>124</v>
       </c>
-      <c r="E155" s="3" t="b">
+      <c r="E155" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
+        <v>198</v>
+      </c>
+      <c r="B156" t="s">
         <v>199</v>
-      </c>
-      <c r="B156" t="s">
-        <v>200</v>
       </c>
       <c r="C156" t="s">
         <v>126</v>
       </c>
-      <c r="E156" s="3" t="b">
+      <c r="E156" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C157" t="s">
         <v>127</v>
       </c>
-      <c r="E157" s="3" t="b">
+      <c r="E157" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C158" t="s">
         <v>128</v>
       </c>
-      <c r="E158" s="3" t="b">
+      <c r="E158" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C159" t="s">
         <v>129</v>
       </c>
-      <c r="E159" s="3" t="b">
+      <c r="E159" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>206</v>
+      </c>
+      <c r="B160" t="s">
         <v>207</v>
-      </c>
-      <c r="B160" t="s">
-        <v>208</v>
       </c>
       <c r="C160" t="s">
         <v>130</v>
       </c>
-      <c r="E160" s="3" t="b">
+      <c r="E160" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>208</v>
+      </c>
+      <c r="B161" t="s">
         <v>209</v>
-      </c>
-      <c r="B161" t="s">
-        <v>210</v>
       </c>
       <c r="C161" t="s">
         <v>131</v>
       </c>
-      <c r="E161" s="3" t="b">
+      <c r="E161" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
+        <v>212</v>
+      </c>
+      <c r="B162" t="s">
         <v>213</v>
-      </c>
-      <c r="B162" t="s">
-        <v>214</v>
       </c>
       <c r="C162" t="s">
         <v>133</v>
       </c>
-      <c r="E162" s="3" t="b">
+      <c r="E162" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B163" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C163" t="s">
         <v>134</v>
       </c>
-      <c r="E163" s="3" t="b">
+      <c r="E163" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
+        <v>216</v>
+      </c>
+      <c r="B164" t="s">
         <v>217</v>
-      </c>
-      <c r="B164" t="s">
-        <v>218</v>
       </c>
       <c r="C164" t="s">
         <v>135</v>
       </c>
-      <c r="E164" s="3" t="b">
+      <c r="E164" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
+        <v>218</v>
+      </c>
+      <c r="B165" t="s">
         <v>219</v>
-      </c>
-      <c r="B165" t="s">
-        <v>220</v>
       </c>
       <c r="C165" t="s">
         <v>136</v>
       </c>
-      <c r="E165" s="3" t="b">
+      <c r="E165" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B166" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C166" t="s">
         <v>137</v>
       </c>
-      <c r="E166" s="3" t="b">
+      <c r="E166" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>222</v>
+      </c>
+      <c r="B167" t="s">
         <v>223</v>
-      </c>
-      <c r="B167" t="s">
-        <v>224</v>
       </c>
       <c r="C167" t="s">
         <v>138</v>
       </c>
-      <c r="E167" s="3" t="b">
+      <c r="E167" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B168" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C168" t="s">
         <v>139</v>
       </c>
-      <c r="E168" s="3" t="b">
+      <c r="E168" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B169" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C169" t="s">
         <v>140</v>
       </c>
-      <c r="E169" s="3" t="b">
+      <c r="E169" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
+        <v>227</v>
+      </c>
+      <c r="B170" t="s">
         <v>228</v>
-      </c>
-      <c r="B170" t="s">
-        <v>229</v>
       </c>
       <c r="C170" t="s">
         <v>141</v>
       </c>
-      <c r="E170" s="3" t="b">
+      <c r="E170" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
+        <v>229</v>
+      </c>
+      <c r="B171" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="C171" t="s">
         <v>142</v>
       </c>
-      <c r="E171" s="3" t="b">
+      <c r="E171" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
+        <v>231</v>
+      </c>
+      <c r="B172" t="s">
         <v>232</v>
-      </c>
-      <c r="B172" t="s">
-        <v>233</v>
       </c>
       <c r="C172" t="s">
         <v>143</v>
       </c>
-      <c r="E172" s="3" t="b">
+      <c r="E172" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B173" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C173" t="s">
         <v>144</v>
       </c>
-      <c r="E173" s="3" t="b">
+      <c r="E173" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
+        <v>237</v>
+      </c>
+      <c r="B174" t="s">
         <v>238</v>
-      </c>
-      <c r="B174" t="s">
-        <v>239</v>
       </c>
       <c r="C174" t="s">
         <v>145</v>
       </c>
-      <c r="E174" s="3" t="b">
+      <c r="E174" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
+        <v>239</v>
+      </c>
+      <c r="B175" t="s">
         <v>240</v>
-      </c>
-      <c r="B175" t="s">
-        <v>241</v>
       </c>
       <c r="C175" t="s">
         <v>146</v>
       </c>
-      <c r="E175" s="3" t="b">
+      <c r="E175" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B176" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C176" t="s">
         <v>147</v>
       </c>
-      <c r="E176" s="3" t="b">
+      <c r="E176" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B177" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C177" t="s">
         <v>148</v>
       </c>
-      <c r="E177" s="3" t="b">
+      <c r="E177" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B178" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C178" t="s">
         <v>149</v>
       </c>
-      <c r="E178" s="3" t="b">
+      <c r="E178" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
+        <v>246</v>
+      </c>
+      <c r="B179" t="s">
         <v>247</v>
-      </c>
-      <c r="B179" t="s">
-        <v>248</v>
       </c>
       <c r="C179" t="s">
         <v>150</v>
       </c>
-      <c r="E179" s="3" t="b">
+      <c r="E179" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B180" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C180" t="s">
         <v>151</v>
       </c>
-      <c r="E180" s="3" t="b">
+      <c r="E180" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
+        <v>249</v>
+      </c>
+      <c r="B181" t="s">
         <v>250</v>
-      </c>
-      <c r="B181" t="s">
-        <v>251</v>
       </c>
       <c r="C181" t="s">
         <v>152</v>
       </c>
-      <c r="E181" s="3" t="b">
+      <c r="E181" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
+        <v>251</v>
+      </c>
+      <c r="B182" t="s">
         <v>252</v>
-      </c>
-      <c r="B182" t="s">
-        <v>253</v>
       </c>
       <c r="C182" t="s">
         <v>153</v>
       </c>
-      <c r="E182" s="3" t="b">
+      <c r="E182" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
+        <v>253</v>
+      </c>
+      <c r="B183" t="s">
         <v>254</v>
-      </c>
-      <c r="B183" t="s">
-        <v>255</v>
       </c>
       <c r="C183" t="s">
         <v>154</v>
       </c>
-      <c r="E183" s="3" t="b">
+      <c r="E183" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
+        <v>255</v>
+      </c>
+      <c r="B184" t="s">
         <v>256</v>
-      </c>
-      <c r="B184" t="s">
-        <v>257</v>
       </c>
       <c r="C184" t="s">
         <v>155</v>
       </c>
-      <c r="E184" s="3" t="b">
+      <c r="E184" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
+        <v>257</v>
+      </c>
+      <c r="B185" t="s">
         <v>258</v>
-      </c>
-      <c r="B185" t="s">
-        <v>259</v>
       </c>
       <c r="C185" t="s">
         <v>155</v>
       </c>
-      <c r="E185" s="3" t="b">
+      <c r="E185" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B186" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C186" t="s">
         <v>156</v>
       </c>
-      <c r="E186" s="3" t="b">
+      <c r="E186" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
+        <v>260</v>
+      </c>
+      <c r="B187" t="s">
         <v>261</v>
-      </c>
-      <c r="B187" t="s">
-        <v>262</v>
       </c>
       <c r="C187" t="s">
         <v>157</v>
       </c>
-      <c r="E187" s="3" t="b">
+      <c r="E187" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B188" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C188" t="s">
         <v>158</v>
       </c>
-      <c r="E188" s="3" t="b">
+      <c r="E188" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B189" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C189" t="s">
         <v>158</v>
       </c>
-      <c r="E189" s="3" t="b">
+      <c r="E189" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
+        <v>265</v>
+      </c>
+      <c r="B190" t="s">
         <v>266</v>
-      </c>
-      <c r="B190" t="s">
-        <v>267</v>
       </c>
       <c r="C190" t="s">
         <v>159</v>
       </c>
-      <c r="E190" s="3" t="b">
+      <c r="E190" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
+        <v>267</v>
+      </c>
+      <c r="B191" t="s">
         <v>268</v>
-      </c>
-      <c r="B191" t="s">
-        <v>269</v>
       </c>
       <c r="C191" t="s">
         <v>160</v>
       </c>
-      <c r="E191" s="3" t="b">
+      <c r="E191" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B192" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C192" t="s">
         <v>161</v>
       </c>
-      <c r="E192" s="3" t="b">
+      <c r="E192" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
+        <v>270</v>
+      </c>
+      <c r="B193" t="s">
         <v>271</v>
-      </c>
-      <c r="B193" t="s">
-        <v>272</v>
       </c>
       <c r="C193" t="s">
         <v>162</v>
       </c>
-      <c r="E193" s="3" t="b">
+      <c r="E193" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B194" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C194" t="s">
         <v>163</v>
       </c>
-      <c r="E194" s="3" t="b">
+      <c r="E194" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B195" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C195" t="s">
         <v>13</v>
       </c>
-      <c r="E195" s="3" t="b">
+      <c r="E195" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
+        <v>235</v>
+      </c>
+      <c r="B196" t="s">
         <v>236</v>
-      </c>
-      <c r="B196" t="s">
-        <v>237</v>
       </c>
       <c r="C196" t="s">
         <v>2</v>
       </c>
-      <c r="E196" s="3" t="b">
+      <c r="E196" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B197" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C197" t="s">
         <v>151</v>
       </c>
-      <c r="E197" s="3" t="b">
+      <c r="E197" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -5234,27 +5233,27 @@
         <v>53</v>
       </c>
       <c r="B198" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C198" t="s">
         <v>115</v>
       </c>
-      <c r="E198" s="3" t="b">
+      <c r="E198" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C199" t="s">
-        <v>175</v>
-      </c>
-      <c r="E199" s="3" t="b">
+        <v>174</v>
+      </c>
+      <c r="E199" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5269,7 +5268,7 @@
       <c r="C200" t="s">
         <v>115</v>
       </c>
-      <c r="E200" s="3" t="b">
+      <c r="E200" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5284,7 +5283,7 @@
       <c r="C201" t="s">
         <v>118</v>
       </c>
-      <c r="E201" s="3" t="b">
+      <c r="E201" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5299,7 +5298,7 @@
       <c r="C202" t="s">
         <v>120</v>
       </c>
-      <c r="E202" s="3" t="b">
+      <c r="E202" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5314,7 +5313,7 @@
       <c r="C203" t="s">
         <v>127</v>
       </c>
-      <c r="E203" s="3" t="b">
+      <c r="E203" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5329,7 +5328,7 @@
       <c r="C204" t="s">
         <v>129</v>
       </c>
-      <c r="E204" s="3" t="b">
+      <c r="E204" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5344,7 +5343,7 @@
       <c r="C205" t="s">
         <v>131</v>
       </c>
-      <c r="E205" s="3" t="b">
+      <c r="E205" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5359,7 +5358,7 @@
       <c r="C206" t="s">
         <v>144</v>
       </c>
-      <c r="E206" s="3" t="b">
+      <c r="E206" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5374,7 +5373,7 @@
       <c r="C207" t="s">
         <v>150</v>
       </c>
-      <c r="E207" s="3" t="b">
+      <c r="E207" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5389,7 +5388,7 @@
       <c r="C208" t="s">
         <v>152</v>
       </c>
-      <c r="E208" s="3" t="b">
+      <c r="E208" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5404,7 +5403,7 @@
       <c r="C209" t="s">
         <v>153</v>
       </c>
-      <c r="E209" s="3" t="b">
+      <c r="E209" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5419,7 +5418,7 @@
       <c r="C210" t="s">
         <v>161</v>
       </c>
-      <c r="E210" s="3" t="b">
+      <c r="E210" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5434,7 +5433,7 @@
       <c r="C211" t="s">
         <v>162</v>
       </c>
-      <c r="E211" s="3" t="b">
+      <c r="E211" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5449,14 +5448,14 @@
       <c r="C212" t="s">
         <v>163</v>
       </c>
-      <c r="E212" s="3" t="b">
+      <c r="E212" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>172</v>
+        <v>506</v>
       </c>
       <c r="B213" t="s">
         <v>170</v>
@@ -5464,7 +5463,7 @@
       <c r="C213" t="s">
         <v>2</v>
       </c>
-      <c r="E213" s="3" t="b">
+      <c r="E213" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5477,9 +5476,9 @@
         <v>171</v>
       </c>
       <c r="C214" t="s">
-        <v>175</v>
-      </c>
-      <c r="E214" s="3" t="b">
+        <v>174</v>
+      </c>
+      <c r="E214" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5492,9 +5491,9 @@
         <v>166</v>
       </c>
       <c r="C215" t="s">
-        <v>175</v>
-      </c>
-      <c r="E215" s="3" t="b">
+        <v>174</v>
+      </c>
+      <c r="E215" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -5507,849 +5506,849 @@
         <v>168</v>
       </c>
       <c r="C216" t="s">
-        <v>175</v>
-      </c>
-      <c r="E216" s="3" t="b">
+        <v>174</v>
+      </c>
+      <c r="E216" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
+        <v>172</v>
+      </c>
+      <c r="B217" t="s">
         <v>173</v>
-      </c>
-      <c r="B217" t="s">
-        <v>174</v>
       </c>
       <c r="C217" t="s">
         <v>2</v>
       </c>
-      <c r="E217" s="3" t="b">
+      <c r="E217" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
+        <v>196</v>
+      </c>
+      <c r="B218" t="s">
         <v>197</v>
-      </c>
-      <c r="B218" t="s">
-        <v>198</v>
       </c>
       <c r="C218" t="s">
         <v>125</v>
       </c>
-      <c r="E218" s="3" t="b">
+      <c r="E218" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
+        <v>210</v>
+      </c>
+      <c r="B219" t="s">
         <v>211</v>
-      </c>
-      <c r="B219" t="s">
-        <v>212</v>
       </c>
       <c r="C219" t="s">
         <v>132</v>
       </c>
-      <c r="E219" s="3" t="b">
+      <c r="E219" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
+        <v>274</v>
+      </c>
+      <c r="B220" t="s">
         <v>275</v>
-      </c>
-      <c r="B220" t="s">
-        <v>276</v>
       </c>
       <c r="C220" t="s">
         <v>115</v>
       </c>
-      <c r="E220" s="3" t="b">
+      <c r="E220" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
+        <v>276</v>
+      </c>
+      <c r="B221" t="s">
         <v>277</v>
-      </c>
-      <c r="B221" t="s">
-        <v>278</v>
       </c>
       <c r="C221" t="s">
         <v>116</v>
       </c>
-      <c r="E221" s="3" t="b">
+      <c r="E221" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
+        <v>278</v>
+      </c>
+      <c r="B222" t="s">
         <v>279</v>
-      </c>
-      <c r="B222" t="s">
-        <v>280</v>
       </c>
       <c r="C222" t="s">
         <v>117</v>
       </c>
-      <c r="E222" s="3" t="b">
+      <c r="E222" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
+        <v>280</v>
+      </c>
+      <c r="B223" t="s">
         <v>281</v>
-      </c>
-      <c r="B223" t="s">
-        <v>282</v>
       </c>
       <c r="C223" t="s">
         <v>118</v>
       </c>
-      <c r="E223" s="3" t="b">
+      <c r="E223" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
+        <v>282</v>
+      </c>
+      <c r="B224" t="s">
         <v>283</v>
-      </c>
-      <c r="B224" t="s">
-        <v>284</v>
       </c>
       <c r="C224" t="s">
         <v>119</v>
       </c>
-      <c r="E224" s="3" t="b">
+      <c r="E224" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B225" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C225" t="s">
         <v>120</v>
       </c>
-      <c r="E225" s="3" t="b">
+      <c r="E225" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
+        <v>286</v>
+      </c>
+      <c r="B226" t="s">
         <v>287</v>
-      </c>
-      <c r="B226" t="s">
-        <v>288</v>
       </c>
       <c r="C226" t="s">
         <v>121</v>
       </c>
-      <c r="E226" s="3" t="b">
+      <c r="E226" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
+        <v>288</v>
+      </c>
+      <c r="B227" t="s">
         <v>289</v>
-      </c>
-      <c r="B227" t="s">
-        <v>290</v>
       </c>
       <c r="C227" t="s">
         <v>122</v>
       </c>
-      <c r="E227" s="3" t="b">
+      <c r="E227" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
+        <v>290</v>
+      </c>
+      <c r="B228" t="s">
         <v>291</v>
-      </c>
-      <c r="B228" t="s">
-        <v>292</v>
       </c>
       <c r="C228" t="s">
         <v>22</v>
       </c>
-      <c r="E228" s="3" t="b">
+      <c r="E228" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B229" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C229" t="s">
         <v>123</v>
       </c>
-      <c r="E229" s="3" t="b">
+      <c r="E229" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
+        <v>294</v>
+      </c>
+      <c r="B230" t="s">
         <v>295</v>
-      </c>
-      <c r="B230" t="s">
-        <v>296</v>
       </c>
       <c r="C230" t="s">
         <v>124</v>
       </c>
-      <c r="E230" s="3" t="b">
+      <c r="E230" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B231" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C231" t="s">
         <v>125</v>
       </c>
-      <c r="E231" s="3" t="b">
+      <c r="E231" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B232" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C232" t="s">
         <v>126</v>
       </c>
-      <c r="E232" s="3" t="b">
+      <c r="E232" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
+        <v>300</v>
+      </c>
+      <c r="B233" t="s">
         <v>301</v>
-      </c>
-      <c r="B233" t="s">
-        <v>302</v>
       </c>
       <c r="C233" t="s">
         <v>127</v>
       </c>
-      <c r="E233" s="3" t="b">
+      <c r="E233" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B234" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C234" t="s">
         <v>128</v>
       </c>
-      <c r="E234" s="3" t="b">
+      <c r="E234" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
+        <v>304</v>
+      </c>
+      <c r="B235" t="s">
         <v>305</v>
-      </c>
-      <c r="B235" t="s">
-        <v>306</v>
       </c>
       <c r="C235" t="s">
         <v>129</v>
       </c>
-      <c r="E235" s="3" t="b">
+      <c r="E235" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
+        <v>306</v>
+      </c>
+      <c r="B236" t="s">
         <v>307</v>
-      </c>
-      <c r="B236" t="s">
-        <v>308</v>
       </c>
       <c r="C236" t="s">
         <v>130</v>
       </c>
-      <c r="E236" s="3" t="b">
+      <c r="E236" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
+        <v>308</v>
+      </c>
+      <c r="B237" t="s">
         <v>309</v>
-      </c>
-      <c r="B237" t="s">
-        <v>310</v>
       </c>
       <c r="C237" t="s">
         <v>131</v>
       </c>
-      <c r="E237" s="3" t="b">
+      <c r="E237" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B238" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C238" t="s">
         <v>132</v>
       </c>
-      <c r="E238" s="3" t="b">
+      <c r="E238" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
+        <v>312</v>
+      </c>
+      <c r="B239" t="s">
         <v>313</v>
-      </c>
-      <c r="B239" t="s">
-        <v>314</v>
       </c>
       <c r="C239" t="s">
         <v>133</v>
       </c>
-      <c r="E239" s="3" t="b">
+      <c r="E239" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
+        <v>314</v>
+      </c>
+      <c r="B240" t="s">
         <v>315</v>
-      </c>
-      <c r="B240" t="s">
-        <v>316</v>
       </c>
       <c r="C240" t="s">
         <v>134</v>
       </c>
-      <c r="E240" s="3" t="b">
+      <c r="E240" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
+        <v>316</v>
+      </c>
+      <c r="B241" t="s">
         <v>317</v>
-      </c>
-      <c r="B241" t="s">
-        <v>318</v>
       </c>
       <c r="C241" t="s">
         <v>135</v>
       </c>
-      <c r="E241" s="3" t="b">
+      <c r="E241" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
+        <v>318</v>
+      </c>
+      <c r="B242" t="s">
         <v>319</v>
-      </c>
-      <c r="B242" t="s">
-        <v>320</v>
       </c>
       <c r="C242" t="s">
         <v>136</v>
       </c>
-      <c r="E242" s="3" t="b">
+      <c r="E242" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
+        <v>320</v>
+      </c>
+      <c r="B243" t="s">
         <v>321</v>
-      </c>
-      <c r="B243" t="s">
-        <v>322</v>
       </c>
       <c r="C243" t="s">
         <v>137</v>
       </c>
-      <c r="E243" s="3" t="b">
+      <c r="E243" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
+        <v>322</v>
+      </c>
+      <c r="B244" t="s">
         <v>323</v>
-      </c>
-      <c r="B244" t="s">
-        <v>324</v>
       </c>
       <c r="C244" t="s">
         <v>138</v>
       </c>
-      <c r="E244" s="3" t="b">
+      <c r="E244" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B245" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C245" t="s">
         <v>139</v>
       </c>
-      <c r="E245" s="3" t="b">
+      <c r="E245" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
+        <v>326</v>
+      </c>
+      <c r="B246" t="s">
         <v>327</v>
-      </c>
-      <c r="B246" t="s">
-        <v>328</v>
       </c>
       <c r="C246" t="s">
         <v>140</v>
       </c>
-      <c r="E246" s="3" t="b">
+      <c r="E246" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B247" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C247" t="s">
         <v>141</v>
       </c>
-      <c r="E247" s="3" t="b">
+      <c r="E247" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
+        <v>330</v>
+      </c>
+      <c r="B248" t="s">
         <v>331</v>
-      </c>
-      <c r="B248" t="s">
-        <v>332</v>
       </c>
       <c r="C248" t="s">
         <v>142</v>
       </c>
-      <c r="E248" s="3" t="b">
+      <c r="E248" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
+        <v>332</v>
+      </c>
+      <c r="B249" t="s">
         <v>333</v>
-      </c>
-      <c r="B249" t="s">
-        <v>334</v>
       </c>
       <c r="C249" t="s">
         <v>143</v>
       </c>
-      <c r="E249" s="3" t="b">
+      <c r="E249" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
+        <v>334</v>
+      </c>
+      <c r="B250" t="s">
         <v>335</v>
-      </c>
-      <c r="B250" t="s">
-        <v>336</v>
       </c>
       <c r="C250" t="s">
         <v>144</v>
       </c>
-      <c r="E250" s="3" t="b">
+      <c r="E250" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
+        <v>336</v>
+      </c>
+      <c r="B251" t="s">
         <v>337</v>
-      </c>
-      <c r="B251" t="s">
-        <v>338</v>
       </c>
       <c r="C251" t="s">
         <v>144</v>
       </c>
-      <c r="E251" s="3" t="b">
+      <c r="E251" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
+        <v>338</v>
+      </c>
+      <c r="B252" t="s">
         <v>339</v>
-      </c>
-      <c r="B252" t="s">
-        <v>340</v>
       </c>
       <c r="C252" t="s">
         <v>145</v>
       </c>
-      <c r="E252" s="3" t="b">
+      <c r="E252" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
+        <v>340</v>
+      </c>
+      <c r="B253" t="s">
         <v>341</v>
-      </c>
-      <c r="B253" t="s">
-        <v>342</v>
       </c>
       <c r="C253" t="s">
         <v>146</v>
       </c>
-      <c r="E253" s="3" t="b">
+      <c r="E253" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B254" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C254" t="s">
         <v>147</v>
       </c>
-      <c r="E254" s="3" t="b">
+      <c r="E254" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
+        <v>344</v>
+      </c>
+      <c r="B255" t="s">
         <v>345</v>
-      </c>
-      <c r="B255" t="s">
-        <v>346</v>
       </c>
       <c r="C255" t="s">
         <v>148</v>
       </c>
-      <c r="E255" s="3" t="b">
+      <c r="E255" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
+        <v>346</v>
+      </c>
+      <c r="B256" t="s">
         <v>347</v>
-      </c>
-      <c r="B256" t="s">
-        <v>348</v>
       </c>
       <c r="C256" t="s">
         <v>149</v>
       </c>
-      <c r="E256" s="3" t="b">
+      <c r="E256" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
+        <v>348</v>
+      </c>
+      <c r="B257" t="s">
         <v>349</v>
-      </c>
-      <c r="B257" t="s">
-        <v>350</v>
       </c>
       <c r="C257" t="s">
         <v>150</v>
       </c>
-      <c r="E257" s="3" t="b">
+      <c r="E257" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B258" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C258" t="s">
         <v>151</v>
       </c>
-      <c r="E258" s="3" t="b">
+      <c r="E258" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
+        <v>352</v>
+      </c>
+      <c r="B259" t="s">
         <v>353</v>
-      </c>
-      <c r="B259" t="s">
-        <v>354</v>
       </c>
       <c r="C259" t="s">
         <v>152</v>
       </c>
-      <c r="E259" s="3" t="b">
+      <c r="E259" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
+        <v>354</v>
+      </c>
+      <c r="B260" t="s">
         <v>355</v>
-      </c>
-      <c r="B260" t="s">
-        <v>356</v>
       </c>
       <c r="C260" t="s">
         <v>152</v>
       </c>
-      <c r="E260" s="3" t="b">
+      <c r="E260" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
+        <v>356</v>
+      </c>
+      <c r="B261" t="s">
         <v>357</v>
-      </c>
-      <c r="B261" t="s">
-        <v>358</v>
       </c>
       <c r="C261" t="s">
         <v>153</v>
       </c>
-      <c r="E261" s="3" t="b">
+      <c r="E261" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
+        <v>358</v>
+      </c>
+      <c r="B262" t="s">
         <v>359</v>
-      </c>
-      <c r="B262" t="s">
-        <v>360</v>
       </c>
       <c r="C262" t="s">
         <v>154</v>
       </c>
-      <c r="E262" s="3" t="b">
+      <c r="E262" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
+        <v>362</v>
+      </c>
+      <c r="B263" t="s">
         <v>363</v>
-      </c>
-      <c r="B263" t="s">
-        <v>364</v>
       </c>
       <c r="C263" t="s">
         <v>155</v>
       </c>
-      <c r="E263" s="3" t="b">
+      <c r="E263" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
+        <v>360</v>
+      </c>
+      <c r="B264" t="s">
         <v>361</v>
-      </c>
-      <c r="B264" t="s">
-        <v>362</v>
       </c>
       <c r="C264" t="s">
         <v>156</v>
       </c>
-      <c r="E264" s="3" t="b">
+      <c r="E264" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B265" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C265" t="s">
         <v>157</v>
       </c>
-      <c r="E265" s="3" t="b">
+      <c r="E265" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B266" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C266" t="s">
         <v>158</v>
       </c>
-      <c r="E266" s="3" t="b">
+      <c r="E266" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
+        <v>368</v>
+      </c>
+      <c r="B267" t="s">
         <v>369</v>
-      </c>
-      <c r="B267" t="s">
-        <v>370</v>
       </c>
       <c r="C267" t="s">
         <v>159</v>
       </c>
-      <c r="E267" s="3" t="b">
+      <c r="E267" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
+        <v>370</v>
+      </c>
+      <c r="B268" t="s">
         <v>371</v>
-      </c>
-      <c r="B268" t="s">
-        <v>372</v>
       </c>
       <c r="C268" t="s">
         <v>160</v>
       </c>
-      <c r="E268" s="3" t="b">
+      <c r="E268" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
+        <v>372</v>
+      </c>
+      <c r="B269" t="s">
         <v>373</v>
-      </c>
-      <c r="B269" t="s">
-        <v>374</v>
       </c>
       <c r="C269" t="s">
         <v>161</v>
       </c>
-      <c r="E269" s="3" t="b">
+      <c r="E269" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
+        <v>374</v>
+      </c>
+      <c r="B270" t="s">
         <v>375</v>
-      </c>
-      <c r="B270" t="s">
-        <v>376</v>
       </c>
       <c r="C270" t="s">
         <v>162</v>
       </c>
-      <c r="E270" s="3" t="b">
+      <c r="E270" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
+        <v>376</v>
+      </c>
+      <c r="B271" t="s">
         <v>377</v>
-      </c>
-      <c r="B271" t="s">
-        <v>378</v>
       </c>
       <c r="C271" t="s">
         <v>163</v>
       </c>
-      <c r="E271" s="3" t="b">
+      <c r="E271" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B272" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C272" t="s">
         <v>13</v>
       </c>
-      <c r="E272" s="3" t="b">
+      <c r="E272" t="b">
         <f>IF(ISNUMBER(SEARCH("gov",Table1[[#This Row],[Link]])),TRUE,FALSE)</f>
         <v>0</v>
       </c>
@@ -6460,17 +6459,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -6485,7 +6484,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
